--- a/校验开发/品牌+规格+最终品名完整版.xlsx
+++ b/校验开发/品牌+规格+最终品名完整版.xlsx
@@ -1056,7 +1056,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NARS空气唇釉thrust</t>
+          <t>NARS空气唇釉tust</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>兰皮气垫新明彩亮润轻垫粉底液</t>
+          <t>皮气垫新明彩亮润轻垫粉底液</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>兰皮气垫新明彩亮润轻垫粉底液</t>
+          <t>皮气垫新明彩亮润轻垫粉底液</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>尼 寄情男士水</t>
+          <t>寄情男士水</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>尼大师蓝标粉底液</t>
+          <t>大师蓝标粉底液</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>尼红管唇釉</t>
+          <t>红管唇釉</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>尼红管唇釉</t>
+          <t>红管唇釉</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>尼红气垫替换芯</t>
+          <t>红气垫替换芯</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>尼权力粉底液</t>
+          <t>权力粉底液</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>尼臻致丝绒哑光唇釉</t>
+          <t>臻致丝绒哑光唇釉</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>尼挚爱哑光唇膏</t>
+          <t>挚爱哑光唇膏</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>仕尼罗河</t>
+          <t>尼罗河</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>波朗 密集修护菁华妆前乳</t>
+          <t>密集修护菁华妆前乳</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>波朗 维他命橘子面霜</t>
+          <t>维他命橘子面霜</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>波朗月光石眼影</t>
+          <t>月光石眼影</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>德无人区玫瑰</t>
+          <t>无人区玫瑰</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>医生美白淡斑精华</t>
+          <t>美白淡斑精华</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>多重防護素顏霜 +/PA++++</t>
+          <t>多重防護素顏霜 + PA++++</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>乐嘉多维面膜涂抹面膜</t>
+          <t>多维面膜涂抹面膜</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>后</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>拱辰享洁面</t>
+          <t>洁面</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>倾色绒雾唇膏（金色短管）</t>
+          <t>倾色绒雾唇膏 金色短管</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>倾色云雾唇釉（红色长管）</t>
+          <t>倾色云雾唇釉 红色长管</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>之谜唇膜</t>
+          <t>唇膜</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>之谜精粹水</t>
+          <t>精粹水</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>之谜精粹水</t>
+          <t>精粹水</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>之谜精华面霜</t>
+          <t>精华面霜</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>之谜绿眼霜</t>
+          <t>绿眼霜</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>之谜面霜</t>
+          <t>面霜</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>之谜气垫</t>
+          <t>气垫</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>拱辰享气韵生水</t>
+          <t>气韵生水</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>拱辰享水妍洁面</t>
+          <t>水妍洁面</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>拱辰享水沄赋活保湿水</t>
+          <t>水沄赋活保湿水</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>拱辰享雪美白水</t>
+          <t>雪美白水</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>希 粉丝绒</t>
+          <t>粉丝绒</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>希 红丝绒口红</t>
+          <t>红丝绒口红</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>希 红丝绒口红</t>
+          <t>红丝绒口红</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>希 小粉皮口红</t>
+          <t>小粉皮口红</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>希 小羊皮</t>
+          <t>小羊皮</t>
         </is>
       </c>
     </row>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>希四宫格散粉色</t>
+          <t>四宫格散粉色</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>诗弹簧水</t>
+          <t>弹簧水</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>诗光芒小瓷瓶精华</t>
+          <t>光芒小瓷瓶精华</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>诗双萃精华九代</t>
+          <t>双萃精华九代</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>诗双萃精华清爽</t>
+          <t>双萃精华清爽</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>诗透亮焕白淡斑乳液</t>
+          <t>透亮焕白淡斑乳液</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>氏白泥面膜</t>
+          <t>白泥面膜</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>氏 高保湿面霜 滋润</t>
+          <t>高保湿面霜 滋润</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>氏 金盏花洁面啫喱</t>
+          <t>金盏花洁面啫喱</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>氏 金盏花面霜</t>
+          <t>金盏花面霜</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>氏 金盏花面霜</t>
+          <t>金盏花面霜</t>
         </is>
       </c>
     </row>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>氏 金盏花爽肤水</t>
+          <t>金盏花爽肤水</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>氏 金盏花植物精华化妆水</t>
+          <t>金盏花植物精华化妆水</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>氏 美白淡斑精华</t>
+          <t>美白淡斑精华</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>氏淡斑精华</t>
+          <t>淡斑精华</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>氏高保湿霜 清爽</t>
+          <t>高保湿霜 清爽</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>氏高保湿滋润面霜滋润</t>
+          <t>高保湿滋润面霜滋润</t>
         </is>
       </c>
     </row>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>氏男士洁面啫喱</t>
+          <t>男士洁面啫喱</t>
         </is>
       </c>
     </row>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>劳伦地球氛</t>
+          <t>地球氛</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>劳伦地球氛</t>
+          <t>地球氛</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>劳伦地球系列氛 安的列斯香根草</t>
+          <t>地球系列氛 安的列斯香根草</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>劳伦地球系列氛 安的列斯香根草</t>
+          <t>地球系列氛 安的列斯香根草</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>劳伦地球系列氛 摩洛哥橙花</t>
+          <t>地球系列氛 摩洛哥橙花</t>
         </is>
       </c>
     </row>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>劳伦地球系列氛 普罗旺斯鼠尾草</t>
+          <t>地球系列氛 普罗旺斯鼠尾草</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>劳伦地球系列氛 普罗旺斯鼠尾草</t>
+          <t>地球系列氛 普罗旺斯鼠尾草</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>劳伦地球系列香氛 澳洲檀木</t>
+          <t>地球系列香氛 澳洲檀木</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>劳伦地球系列香氛 澳洲檀木</t>
+          <t>地球系列香氛 澳洲檀木</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>劳伦俱乐部香水型</t>
+          <t>俱乐部香水型</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>劳伦俱乐部香水型</t>
+          <t>俱乐部香水型</t>
         </is>
       </c>
     </row>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>得塑颜修复A醇精华</t>
+          <t>塑颜修复A醇精华</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>薇奇净颜美肌洁面乳</t>
+          <t>净颜美肌洁面乳</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>VICHY洗发水绿标硫化硒去屑止痒控油洗发乳</t>
+          <t>洗发水绿标硫化硒去屑止痒控油洗发乳</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>儿山茶花柔和净肤泡沫 洁面 女款 清爽</t>
+          <t>山茶花柔和净肤泡沫 洁面 女款 清爽</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6396,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>兰黛 第七代 小棕瓶</t>
+          <t>第七代 小棕瓶</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>兰黛 净莹柔肤洁面乳（蓝洁面）</t>
+          <t>净莹柔肤洁面乳 蓝洁面</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>兰黛DW</t>
+          <t>DW</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>兰黛大棕罐膜霜</t>
+          <t>大棕罐膜霜</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>兰黛红石榴洁面</t>
+          <t>洁面</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>兰黛第七代特润小棕瓶（）</t>
+          <t>第七代特润小棕瓶</t>
         </is>
       </c>
     </row>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>兰黛线雕精华（）</t>
+          <t>线雕精华</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>兰黛小棕瓶眼霜</t>
+          <t>小棕瓶眼霜</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>兰黛智妍晚霜</t>
+          <t>智妍晚霜</t>
         </is>
       </c>
     </row>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>纱 三色遮瑕</t>
+          <t>三色遮瑕</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>堂安耐晒</t>
+          <t>安耐晒</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>堂百优面霜</t>
+          <t>百优面霜</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6756,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>堂蓝胖子</t>
+          <t>蓝胖子</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>堂蓝胖子防晒</t>
+          <t>蓝胖子防晒</t>
         </is>
       </c>
     </row>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>堂蓝胖子防晒（）</t>
+          <t>蓝胖子防晒</t>
         </is>
       </c>
     </row>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>堂琉璃洁面</t>
+          <t>琉璃洁面</t>
         </is>
       </c>
     </row>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>堂琉璃洁面</t>
+          <t>琉璃洁面</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>堂琉璃爽肤水</t>
+          <t>琉璃爽肤水</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>堂男生爽肤水</t>
+          <t>男生爽肤水</t>
         </is>
       </c>
     </row>
@@ -6966,7 +6966,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>堂男士洁面乳</t>
+          <t>男士洁面乳</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>堂男士乳液</t>
+          <t>男士乳液</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>堂悦微清爽水（）</t>
+          <t>悦微清爽水</t>
         </is>
       </c>
     </row>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>堂悦微滋润水（）</t>
+          <t>悦微滋润水</t>
         </is>
       </c>
     </row>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>堂悦薇纯A小针管眼霜</t>
+          <t>悦薇纯A小针管眼霜</t>
         </is>
       </c>
     </row>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>堂悦薇滋润乳（）</t>
+          <t>悦薇滋润乳</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>堂悦薇清爽乳（）</t>
+          <t>悦薇清爽乳</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>珑 蓝风铃香水</t>
+          <t>蓝风铃香水</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>珑鼠尾草与海盐香水</t>
+          <t>鼠尾草与海盐香水</t>
         </is>
       </c>
     </row>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>尼大师蓝标粉底液</t>
+          <t>大师蓝标粉底液</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>尼权力粉底</t>
+          <t>权力粉底</t>
         </is>
       </c>
     </row>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>尼权力粉底</t>
+          <t>权力粉底</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>尼「大师」锁光粉底液</t>
+          <t>「大师」锁光粉底液</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>尼气垫替换芯</t>
+          <t>气垫替换芯</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>马来西亚OLDTOWN进口白咖啡天然庶糖</t>
+          <t>马来西亚进口白咖啡天然庶糖</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>兰黛红石榴洁面</t>
+          <t>洁面</t>
         </is>
       </c>
     </row>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>堂/SHISEIDO红腰子精华（）</t>
+          <t>红腰子精华</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>堂/ SHISEIDO时光大琉璃水（）</t>
+          <t>时光大琉璃水</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>堂/SHISEIDO悦薇大抗糖面霜（清爽）</t>
+          <t>悦薇大抗糖面霜 清爽</t>
         </is>
       </c>
     </row>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>堂/SHISEIDO琉璃晚霜（）</t>
+          <t>琉璃晚霜</t>
         </is>
       </c>
     </row>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>堂/SHISEIDO百优面霜</t>
+          <t>百优面霜</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>哲 爱罗斯爱神男士香水</t>
+          <t>爱罗斯爱神男士香水</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>哲 爱罗斯爱神男士香水 简装</t>
+          <t>爱罗斯爱神男士香水 简装</t>
         </is>
       </c>
     </row>
@@ -8076,7 +8076,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>哲 追梦人男士水</t>
+          <t>追梦人男士水</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>萨迪 雅逸玫瑰女士香水</t>
+          <t>雅逸玫瑰女士香水</t>
         </is>
       </c>
     </row>
@@ -8226,7 +8226,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>杜夫 冷水男士香水 加强版</t>
+          <t>冷水男士香水 加强版</t>
         </is>
       </c>
     </row>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>诗 双萃眼霜</t>
+          <t>双萃眼霜</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>诗 双萃第代</t>
+          <t>双萃第代</t>
         </is>
       </c>
     </row>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>诗 棉花籽洁面</t>
+          <t>棉花籽洁面</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>诗 抚纹油</t>
+          <t>抚纹油</t>
         </is>
       </c>
     </row>
@@ -8406,7 +8406,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>诗 双萃第代</t>
+          <t>双萃第代</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>丹樱花护手霜</t>
+          <t>樱花护手霜</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>丹乳木果身体乳</t>
+          <t>乳木果身体乳</t>
         </is>
       </c>
     </row>
@@ -8496,7 +8496,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>丹玫瑰身体乳</t>
+          <t>玫瑰身体乳</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8526,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>之谜洁面</t>
+          <t>洁面</t>
         </is>
       </c>
     </row>
@@ -8616,7 +8616,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>FERRERO ROCHER 罗榛果巧克力制品</t>
+          <t>ROCHER 罗榛果巧克力制品</t>
         </is>
       </c>
     </row>
@@ -8636,7 +8636,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>雅诗兰黛</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>红石榴面霜</t>
+          <t>面霜</t>
         </is>
       </c>
     </row>
@@ -8676,7 +8676,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>兰爱心黑管唇釉</t>
+          <t>爱心黑管唇釉</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>兰黑色皮革气垫</t>
+          <t>黑色皮革气垫</t>
         </is>
       </c>
     </row>
@@ -8736,7 +8736,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>兰黑色皮革气垫替换装</t>
+          <t>黑色皮革气垫替换装</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>小灯泡（款）</t>
+          <t>小灯泡 款</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>泉男士水动力乳液</t>
+          <t>男士水动力乳液</t>
         </is>
       </c>
     </row>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>兰女神逆龄粉底液</t>
+          <t>女神逆龄粉底液</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>城市牛郎眼影</t>
+          <t>牛郎眼影</t>
         </is>
       </c>
     </row>
@@ -9156,7 +9156,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>仕大地水</t>
+          <t>大地水</t>
         </is>
       </c>
     </row>
@@ -9216,7 +9216,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>兰黛 鲜活亮采红石榴倍润水</t>
+          <t>鲜活亮采倍润水</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>兰夜皇后</t>
+          <t>夜皇后</t>
         </is>
       </c>
     </row>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>兰恒久粉底液粉盖</t>
+          <t>恒久粉底液粉盖</t>
         </is>
       </c>
     </row>
@@ -9306,7 +9306,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>兰恒久粉底液粉盖</t>
+          <t>恒久粉底液粉盖</t>
         </is>
       </c>
     </row>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>兰 明彩粉光轻垫粉底液 粉气垫 CN</t>
+          <t>明彩粉光轻垫粉底液 粉气垫 CN</t>
         </is>
       </c>
     </row>
@@ -9396,7 +9396,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>堂蓝胖子防晒</t>
+          <t>蓝胖子防晒</t>
         </is>
       </c>
     </row>
@@ -9426,7 +9426,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>尼权力粉底</t>
+          <t>权力粉底</t>
         </is>
       </c>
     </row>
@@ -9636,7 +9636,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>希四宫格散粉色（）</t>
+          <t>四宫格散粉色</t>
         </is>
       </c>
     </row>
@@ -9726,7 +9726,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>GUCCI绮梦馥栀</t>
+          <t>绮梦馥栀</t>
         </is>
       </c>
     </row>
@@ -9756,7 +9756,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>GUCCI花悦绽放</t>
+          <t>花悦绽放</t>
         </is>
       </c>
     </row>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>GUCCI绮梦木兰型</t>
+          <t>绮梦木兰型</t>
         </is>
       </c>
     </row>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>GUCCI绮梦栀子花型</t>
+          <t>绮梦栀子花型</t>
         </is>
       </c>
     </row>
@@ -9846,7 +9846,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>GUCCI绮梦香草兰香</t>
+          <t>绮梦香草兰香</t>
         </is>
       </c>
     </row>
@@ -9876,7 +9876,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>GUCCI绮梦香草兰香</t>
+          <t>绮梦香草兰香</t>
         </is>
       </c>
     </row>
@@ -10056,7 +10056,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>女士洗面奶/支</t>
+          <t>女士洗面奶 支</t>
         </is>
       </c>
     </row>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Whoo天气丹PRO乳</t>
+          <t>天气丹PRO乳</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>拱辰享美黄金气垫+替换装</t>
+          <t>美黄金气垫+替换装</t>
         </is>
       </c>
     </row>
@@ -10266,7 +10266,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>TOMFORD幻魅四色眼影盘 玫瑰晶石</t>
+          <t>幻魅四色眼影盘 玫瑰晶石</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>希粉丝绒</t>
+          <t>粉丝绒</t>
         </is>
       </c>
     </row>
@@ -10416,7 +10416,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>兰爱心黑管唇釉</t>
+          <t>爱心黑管唇釉</t>
         </is>
       </c>
     </row>
@@ -10446,7 +10446,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>兰黛红石榴洁面</t>
+          <t>洁面</t>
         </is>
       </c>
     </row>
@@ -10476,7 +10476,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>兰黛红石榴水</t>
+          <t>水</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>诗西柚香皂</t>
+          <t>西柚香皂</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>诗玫瑰花瓣水</t>
+          <t>玫瑰花瓣水</t>
         </is>
       </c>
     </row>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>诗红茶紧致面霜</t>
+          <t>红茶紧致面霜</t>
         </is>
       </c>
     </row>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>诗睡莲日霜</t>
+          <t>睡莲日霜</t>
         </is>
       </c>
     </row>
@@ -10686,7 +10686,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>诗玫瑰保湿面霜</t>
+          <t>玫瑰保湿面霜</t>
         </is>
       </c>
     </row>
@@ -10716,7 +10716,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>诗小苍兰香皂</t>
+          <t>小苍兰香皂</t>
         </is>
       </c>
     </row>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>兰黛白金粉底液</t>
+          <t>白金粉底液</t>
         </is>
       </c>
     </row>
@@ -10776,7 +10776,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>诗红茶精粹水</t>
+          <t>红茶精粹水</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>兰黛白金粉底液</t>
+          <t>白金粉底液</t>
         </is>
       </c>
     </row>
@@ -10836,7 +10836,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>诗美白滋润水</t>
+          <t>美白滋润水</t>
         </is>
       </c>
     </row>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>诗焕颜紧致晚霜</t>
+          <t>焕颜紧致晚霜</t>
         </is>
       </c>
     </row>
@@ -10896,7 +10896,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>兰黛多效智妍乳霜清爽</t>
+          <t>多效智妍乳霜清爽</t>
         </is>
       </c>
     </row>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>氏男士乳液</t>
+          <t>男士乳液</t>
         </is>
       </c>
     </row>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>氏果冻清爽高保湿霜/瓶</t>
+          <t>果冻清爽高保湿霜 瓶</t>
         </is>
       </c>
     </row>
@@ -11046,7 +11046,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>诗第九代全新双萃焕活修护精华</t>
+          <t>第九代全新双萃焕活修护精华</t>
         </is>
       </c>
     </row>
@@ -11076,7 +11076,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>堂安耐晒</t>
+          <t>安耐晒</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>未匹配</t>
+          <t>安耐晒</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>安耐晒金钻高效防晒</t>
+          <t>金钻高效防晒</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>兰黛樱花微精华原生液</t>
+          <t>樱花微精华原生液</t>
         </is>
       </c>
     </row>
@@ -11166,7 +11166,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>兰小金条细管口红复古正红色</t>
+          <t>小金条细管口红复古正红色</t>
         </is>
       </c>
     </row>
@@ -11196,7 +11196,7 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>布朗舒缓卸妆洁面油</t>
+          <t>舒缓卸妆洁面油</t>
         </is>
       </c>
     </row>
@@ -11226,7 +11226,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>诗双萃焕活修护精华露</t>
+          <t>双萃焕活修护精华露</t>
         </is>
       </c>
     </row>
@@ -11256,7 +11256,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>尼权力口红</t>
+          <t>权力口红</t>
         </is>
       </c>
     </row>
@@ -11286,7 +11286,7 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>兰黑金方管</t>
+          <t>黑金方管</t>
         </is>
       </c>
     </row>
@@ -11316,7 +11316,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>兰黑金方管</t>
+          <t>黑金方管</t>
         </is>
       </c>
     </row>
@@ -11346,7 +11346,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>兰黑金方管</t>
+          <t>黑金方管</t>
         </is>
       </c>
     </row>
@@ -11376,7 +11376,7 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>兰银管</t>
+          <t>银管</t>
         </is>
       </c>
     </row>
@@ -11436,7 +11436,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>之谜 臻璨焕活精华油 （万能油）</t>
+          <t>臻璨焕活精华油 万能油</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>兰黛红石榴能量水清爽型</t>
+          <t>能量水清爽型</t>
         </is>
       </c>
     </row>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>尼大师粉底液</t>
+          <t>大师粉底液</t>
         </is>
       </c>
     </row>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>GUCCI 香水 茉莉</t>
+          <t>香水 茉莉</t>
         </is>
       </c>
     </row>
@@ -11796,7 +11796,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>李先生的花园(Le Jardin de Monsieur Li)，水，</t>
+          <t>李先生的花园 Le Jardin de Monsieur Li ，水，</t>
         </is>
       </c>
     </row>
@@ -11826,7 +11826,7 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>绯红火参古龙水（Eau de rhubarbe écarlate）, 古龍水,</t>
+          <t>绯红火参古龙水 Eau de rhubarbe écarlate , 古龍水,</t>
         </is>
       </c>
     </row>
@@ -11916,7 +11916,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>LAMER之谜调理焕肤液</t>
+          <t>调理焕肤液</t>
         </is>
       </c>
     </row>
@@ -12036,7 +12036,7 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>兰黛 红石榴面霜</t>
+          <t>面霜</t>
         </is>
       </c>
     </row>
@@ -12066,7 +12066,7 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>兰黛 红石榴洁面</t>
+          <t>洁面</t>
         </is>
       </c>
     </row>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>堂/SHISEIDO红腰子洁面</t>
+          <t>红腰子洁面</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>堂/SHISEIDO悦薇抗糖眼霜（）</t>
+          <t>悦薇抗糖眼霜</t>
         </is>
       </c>
     </row>
@@ -12156,7 +12156,7 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>堂/SHISEIDO盼丽风姿眼霜（）</t>
+          <t>盼丽风姿眼霜</t>
         </is>
       </c>
     </row>
@@ -12186,7 +12186,7 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>兰黛 DW持妆粉底液</t>
+          <t>DW持妆粉底液</t>
         </is>
       </c>
     </row>
@@ -12216,7 +12216,7 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>兰黛 DW持妆粉底液</t>
+          <t>DW持妆粉底液</t>
         </is>
       </c>
     </row>
@@ -12246,7 +12246,7 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>兰黛 DW持妆粉底液</t>
+          <t>DW持妆粉底液</t>
         </is>
       </c>
     </row>
@@ -12306,7 +12306,7 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>Skin Veil Base_EX No. 紫色</t>
+          <t>Skin Veil Base EX No. 紫色</t>
         </is>
       </c>
     </row>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Skin Veil Base_EX No. 绿色</t>
+          <t>Skin Veil Base EX No. 绿色</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>堂 悦薇大抗糖滋润面霜（）</t>
+          <t>悦薇大抗糖滋润面霜</t>
         </is>
       </c>
     </row>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>拱辰享洁面泡沫/支 （新条码）</t>
+          <t>洁面泡沫 支 新条码</t>
         </is>
       </c>
     </row>
@@ -12456,7 +12456,7 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>SHISEIDO堂红腰子精华</t>
+          <t>红腰子精华</t>
         </is>
       </c>
     </row>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>丽白茶</t>
+          <t>白茶</t>
         </is>
       </c>
     </row>
@@ -12726,7 +12726,7 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>珑英国梨与豌豆花香水</t>
+          <t>英国梨与豌豆花香水</t>
         </is>
       </c>
     </row>
@@ -12846,7 +12846,7 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>AFTERGLOW LIQUID BLUSH - INSATIABLE</t>
+          <t>AFTERGLOW LIQUID BLUSH INSATIABLE</t>
         </is>
       </c>
     </row>
@@ -12966,7 +12966,7 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>AFTER GLOW LIQUID BLUSH -WANDERLUST</t>
+          <t>AFTER GLOW LIQUID BLUSH WANDERLUST</t>
         </is>
       </c>
     </row>
@@ -13026,7 +13026,7 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>雅紫熨斗 第三代</t>
+          <t>紫熨斗 第三代</t>
         </is>
       </c>
     </row>
